--- a/docs/01_MODULO_A_DESPLIEGUE/RehniMarket_Pruebas_Aceptacion_20_Casos(1).xlsx
+++ b/docs/01_MODULO_A_DESPLIEGUE/RehniMarket_Pruebas_Aceptacion_20_Casos(1).xlsx
@@ -792,12 +792,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>324805</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>63498</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2086605" cy="613832"/>
+    <xdr:ext cx="1654895" cy="486833"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="285281984" name=""/>
@@ -811,8 +811,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm flipH="0" flipV="0">
-          <a:off x="25820055" y="63498"/>
-          <a:ext cx="2086606" cy="613833"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1654895" cy="486833"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
